--- a/Data Sources.xlsx
+++ b/Data Sources.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/will/Documents/DataSci-Assignment-1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{74A00D51-B2FC-5D43-B8EF-949BD66E87B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6CD5B8C-C127-E74F-A844-33C4D2A5322D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{4FC011C9-1206-0647-BF8A-ECF4AE7C673F}"/>
   </bookViews>
@@ -37,30 +37,8 @@
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6516" uniqueCount="202">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6503" uniqueCount="200">
   <si>
     <t>App</t>
   </si>
@@ -659,12 +637,6 @@
     <t>Samsung Galaxy S21</t>
   </si>
   <si>
-    <t>Duration</t>
-  </si>
-  <si>
-    <t>Notfications</t>
-  </si>
-  <si>
     <t>AppClean</t>
   </si>
 </sst>
@@ -688,18 +660,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD9D9D9"/>
-        <bgColor rgb="FFD9D9D9"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -718,7 +684,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1137,7 +1103,7 @@
     <col min="13" max="13" width="15.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="2" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B2" t="s">
         <v>3</v>
       </c>
@@ -1157,22 +1123,10 @@
         <v>5</v>
       </c>
       <c r="H2" t="s">
-        <v>201</v>
-      </c>
-      <c r="J2" t="s">
-        <v>0</v>
-      </c>
-      <c r="K2" t="s">
         <v>199</v>
       </c>
-      <c r="L2" t="s">
-        <v>200</v>
-      </c>
-      <c r="M2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="2:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="3" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B3" s="1">
         <v>46082</v>
       </c>
@@ -1195,24 +1149,8 @@
         <f>TRIM(Table1[[#This Row],[App]])</f>
         <v>Youtube</v>
       </c>
-      <c r="J3" t="str" cm="1">
-        <f t="array" ref="J3:J28">_xlfn.UNIQUE(TRIM(Table1[App]))</f>
-        <v>Youtube</v>
-      </c>
-      <c r="K3">
-        <f>SUMIF(Table1[AppClean], $J3, Table1[Day Duration (Minutes)])</f>
-        <v>71</v>
-      </c>
-      <c r="L3">
-        <f>SUMIF(Table1[AppClean], $J3, Table1[Notifications])</f>
-        <v>0</v>
-      </c>
-      <c r="M3">
-        <f>SUMIF(Table1[AppClean], $J3, Table1[Times Opened])</f>
-        <v>21</v>
-      </c>
-    </row>
-    <row r="4" spans="2:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="4" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B4" s="1">
         <v>46082</v>
       </c>
@@ -1235,23 +1173,8 @@
         <f>TRIM(Table1[[#This Row],[App]])</f>
         <v>Firefox</v>
       </c>
-      <c r="J4" t="str">
-        <v>Firefox</v>
-      </c>
-      <c r="K4">
-        <f>SUMIF(Table1[AppClean], $J4, Table1[Day Duration (Minutes)])</f>
-        <v>618</v>
-      </c>
-      <c r="L4">
-        <f>SUMIF(Table1[AppClean], $J4, Table1[Notifications])</f>
-        <v>118</v>
-      </c>
-      <c r="M4">
-        <f>SUMIF(Table1[AppClean], $J4, Table1[Times Opened])</f>
-        <v>195</v>
-      </c>
-    </row>
-    <row r="5" spans="2:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="5" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B5" s="1">
         <v>46082</v>
       </c>
@@ -1274,23 +1197,8 @@
         <f>TRIM(Table1[[#This Row],[App]])</f>
         <v>Instagram</v>
       </c>
-      <c r="J5" t="str">
-        <v>Instagram</v>
-      </c>
-      <c r="K5">
-        <f>SUMIF(Table1[AppClean], $J5, Table1[Day Duration (Minutes)])</f>
-        <v>1172</v>
-      </c>
-      <c r="L5">
-        <f>SUMIF(Table1[AppClean], $J5, Table1[Notifications])</f>
-        <v>328</v>
-      </c>
-      <c r="M5">
-        <f>SUMIF(Table1[AppClean], $J5, Table1[Times Opened])</f>
-        <v>489</v>
-      </c>
-    </row>
-    <row r="6" spans="2:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="6" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B6" s="1">
         <v>46082</v>
       </c>
@@ -1313,23 +1221,9 @@
         <f>TRIM(Table1[[#This Row],[App]])</f>
         <v>Whatsapp</v>
       </c>
-      <c r="J6" s="1" t="str">
-        <v>Whatsapp</v>
-      </c>
-      <c r="K6">
-        <f>SUMIF(Table1[AppClean], $J6, Table1[Day Duration (Minutes)])</f>
-        <v>9</v>
-      </c>
-      <c r="L6">
-        <f>SUMIF(Table1[AppClean], $J6, Table1[Notifications])</f>
-        <v>41</v>
-      </c>
-      <c r="M6">
-        <f>SUMIF(Table1[AppClean], $J6, Table1[Times Opened])</f>
-        <v>30</v>
-      </c>
-    </row>
-    <row r="7" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="J6" s="1"/>
+    </row>
+    <row r="7" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B7" s="1">
         <v>46082</v>
       </c>
@@ -1352,23 +1246,8 @@
         <f>TRIM(Table1[[#This Row],[App]])</f>
         <v>Outlook</v>
       </c>
-      <c r="J7" t="str">
-        <v>Outlook</v>
-      </c>
-      <c r="K7">
-        <f>SUMIF(Table1[AppClean], $J7, Table1[Day Duration (Minutes)])</f>
-        <v>6</v>
-      </c>
-      <c r="L7">
-        <f>SUMIF(Table1[AppClean], $J7, Table1[Notifications])</f>
-        <v>2</v>
-      </c>
-      <c r="M7">
-        <f>SUMIF(Table1[AppClean], $J7, Table1[Times Opened])</f>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="8" spans="2:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="8" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B8" s="1">
         <v>46082</v>
       </c>
@@ -1391,23 +1270,8 @@
         <f>TRIM(Table1[[#This Row],[App]])</f>
         <v>Signal</v>
       </c>
-      <c r="J8" t="str">
-        <v>Signal</v>
-      </c>
-      <c r="K8">
-        <f>SUMIF(Table1[AppClean], $J8, Table1[Day Duration (Minutes)])</f>
-        <v>101</v>
-      </c>
-      <c r="L8">
-        <f>SUMIF(Table1[AppClean], $J8, Table1[Notifications])</f>
-        <v>745</v>
-      </c>
-      <c r="M8">
-        <f>SUMIF(Table1[AppClean], $J8, Table1[Times Opened])</f>
-        <v>398</v>
-      </c>
-    </row>
-    <row r="9" spans="2:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="9" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B9" s="1">
         <v>46082</v>
       </c>
@@ -1430,23 +1294,8 @@
         <f>TRIM(Table1[[#This Row],[App]])</f>
         <v>Phone</v>
       </c>
-      <c r="J9" t="str">
-        <v>Phone</v>
-      </c>
-      <c r="K9">
-        <f>SUMIF(Table1[AppClean], $J9, Table1[Day Duration (Minutes)])</f>
-        <v>22</v>
-      </c>
-      <c r="L9">
-        <f>SUMIF(Table1[AppClean], $J9, Table1[Notifications])</f>
-        <v>19</v>
-      </c>
-      <c r="M9">
-        <f>SUMIF(Table1[AppClean], $J9, Table1[Times Opened])</f>
-        <v>34</v>
-      </c>
-    </row>
-    <row r="10" spans="2:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="10" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B10" s="1">
         <v>46083</v>
       </c>
@@ -1469,23 +1318,8 @@
         <f>TRIM(Table1[[#This Row],[App]])</f>
         <v>Jellyfin</v>
       </c>
-      <c r="J10" t="str">
-        <v>Jellyfin</v>
-      </c>
-      <c r="K10">
-        <f>SUMIF(Table1[AppClean], $J10, Table1[Day Duration (Minutes)])</f>
-        <v>225</v>
-      </c>
-      <c r="L10">
-        <f>SUMIF(Table1[AppClean], $J10, Table1[Notifications])</f>
-        <v>3</v>
-      </c>
-      <c r="M10">
-        <f>SUMIF(Table1[AppClean], $J10, Table1[Times Opened])</f>
-        <v>34</v>
-      </c>
-    </row>
-    <row r="11" spans="2:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="11" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B11" s="1">
         <v>46083</v>
       </c>
@@ -1508,23 +1342,8 @@
         <f>TRIM(Table1[[#This Row],[App]])</f>
         <v>Instagram</v>
       </c>
-      <c r="J11" t="str">
-        <v>Aliexpress</v>
-      </c>
-      <c r="K11">
-        <f>SUMIF(Table1[AppClean], $J11, Table1[Day Duration (Minutes)])</f>
-        <v>13</v>
-      </c>
-      <c r="L11">
-        <f>SUMIF(Table1[AppClean], $J11, Table1[Notifications])</f>
-        <v>0</v>
-      </c>
-      <c r="M11">
-        <f>SUMIF(Table1[AppClean], $J11, Table1[Times Opened])</f>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="12" spans="2:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="12" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B12" s="1">
         <v>46083</v>
       </c>
@@ -1547,23 +1366,8 @@
         <f>TRIM(Table1[[#This Row],[App]])</f>
         <v>Firefox</v>
       </c>
-      <c r="J12" t="str">
-        <v>Foldersync</v>
-      </c>
-      <c r="K12">
-        <f>SUMIF(Table1[AppClean], $J12, Table1[Day Duration (Minutes)])</f>
-        <v>8</v>
-      </c>
-      <c r="L12">
-        <f>SUMIF(Table1[AppClean], $J12, Table1[Notifications])</f>
-        <v>3</v>
-      </c>
-      <c r="M12">
-        <f>SUMIF(Table1[AppClean], $J12, Table1[Times Opened])</f>
-        <v>6</v>
-      </c>
-    </row>
-    <row r="13" spans="2:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="13" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B13" s="1">
         <v>46083</v>
       </c>
@@ -1586,23 +1390,8 @@
         <f>TRIM(Table1[[#This Row],[App]])</f>
         <v>Aliexpress</v>
       </c>
-      <c r="J13" t="str">
-        <v>NASDeck</v>
-      </c>
-      <c r="K13">
-        <f>SUMIF(Table1[AppClean], $J13, Table1[Day Duration (Minutes)])</f>
-        <v>4</v>
-      </c>
-      <c r="L13">
-        <f>SUMIF(Table1[AppClean], $J13, Table1[Notifications])</f>
-        <v>0</v>
-      </c>
-      <c r="M13">
-        <f>SUMIF(Table1[AppClean], $J13, Table1[Times Opened])</f>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="14" spans="2:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="14" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B14" s="1">
         <v>46083</v>
       </c>
@@ -1625,23 +1414,8 @@
         <f>TRIM(Table1[[#This Row],[App]])</f>
         <v>Foldersync</v>
       </c>
-      <c r="J14" t="str">
-        <v>NFC Tools</v>
-      </c>
-      <c r="K14">
-        <f>SUMIF(Table1[AppClean], $J14, Table1[Day Duration (Minutes)])</f>
-        <v>9</v>
-      </c>
-      <c r="L14">
-        <f>SUMIF(Table1[AppClean], $J14, Table1[Notifications])</f>
-        <v>0</v>
-      </c>
-      <c r="M14">
-        <f>SUMIF(Table1[AppClean], $J14, Table1[Times Opened])</f>
-        <v>6</v>
-      </c>
-    </row>
-    <row r="15" spans="2:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="15" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B15" s="1">
         <v>46083</v>
       </c>
@@ -1664,23 +1438,8 @@
         <f>TRIM(Table1[[#This Row],[App]])</f>
         <v>Signal</v>
       </c>
-      <c r="J15" t="str">
-        <v>UP Banking</v>
-      </c>
-      <c r="K15">
-        <f>SUMIF(Table1[AppClean], $J15, Table1[Day Duration (Minutes)])</f>
-        <v>4</v>
-      </c>
-      <c r="L15">
-        <f>SUMIF(Table1[AppClean], $J15, Table1[Notifications])</f>
-        <v>4</v>
-      </c>
-      <c r="M15">
-        <f>SUMIF(Table1[AppClean], $J15, Table1[Times Opened])</f>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16" spans="2:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="16" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B16" s="1">
         <v>46083</v>
       </c>
@@ -1703,23 +1462,8 @@
         <f>TRIM(Table1[[#This Row],[App]])</f>
         <v>NASDeck</v>
       </c>
-      <c r="J16" t="str">
-        <v>Google Maps</v>
-      </c>
-      <c r="K16">
-        <f>SUMIF(Table1[AppClean], $J16, Table1[Day Duration (Minutes)])</f>
-        <v>87</v>
-      </c>
-      <c r="L16">
-        <f>SUMIF(Table1[AppClean], $J16, Table1[Notifications])</f>
-        <v>10</v>
-      </c>
-      <c r="M16">
-        <f>SUMIF(Table1[AppClean], $J16, Table1[Times Opened])</f>
-        <v>16</v>
-      </c>
-    </row>
-    <row r="17" spans="2:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="17" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B17" s="1">
         <v>46083</v>
       </c>
@@ -1742,23 +1486,8 @@
         <f>TRIM(Table1[[#This Row],[App]])</f>
         <v>Phone</v>
       </c>
-      <c r="J17" t="str">
-        <v>ChatGPT</v>
-      </c>
-      <c r="K17">
-        <f>SUMIF(Table1[AppClean], $J17, Table1[Day Duration (Minutes)])</f>
-        <v>54</v>
-      </c>
-      <c r="L17">
-        <f>SUMIF(Table1[AppClean], $J17, Table1[Notifications])</f>
-        <v>0</v>
-      </c>
-      <c r="M17">
-        <f>SUMIF(Table1[AppClean], $J17, Table1[Times Opened])</f>
-        <v>43</v>
-      </c>
-    </row>
-    <row r="18" spans="2:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="18" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B18" s="1">
         <v>46084</v>
       </c>
@@ -1781,23 +1510,8 @@
         <f>TRIM(Table1[[#This Row],[App]])</f>
         <v>Instagram</v>
       </c>
-      <c r="J18" t="str">
-        <v>Files</v>
-      </c>
-      <c r="K18">
-        <f>SUMIF(Table1[AppClean], $J18, Table1[Day Duration (Minutes)])</f>
-        <v>2</v>
-      </c>
-      <c r="L18">
-        <f>SUMIF(Table1[AppClean], $J18, Table1[Notifications])</f>
-        <v>0</v>
-      </c>
-      <c r="M18">
-        <f>SUMIF(Table1[AppClean], $J18, Table1[Times Opened])</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="19" spans="2:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="19" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B19" s="1">
         <v>46084</v>
       </c>
@@ -1820,23 +1534,8 @@
         <f>TRIM(Table1[[#This Row],[App]])</f>
         <v>Firefox</v>
       </c>
-      <c r="J19" t="str">
-        <v>Gmail</v>
-      </c>
-      <c r="K19">
-        <f>SUMIF(Table1[AppClean], $J19, Table1[Day Duration (Minutes)])</f>
-        <v>3</v>
-      </c>
-      <c r="L19">
-        <f>SUMIF(Table1[AppClean], $J19, Table1[Notifications])</f>
-        <v>14</v>
-      </c>
-      <c r="M19">
-        <f>SUMIF(Table1[AppClean], $J19, Table1[Times Opened])</f>
-        <v>8</v>
-      </c>
-    </row>
-    <row r="20" spans="2:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="20" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B20" s="1">
         <v>46084</v>
       </c>
@@ -1859,23 +1558,8 @@
         <f>TRIM(Table1[[#This Row],[App]])</f>
         <v>NFC Tools</v>
       </c>
-      <c r="J20" t="str">
-        <v>Gallery</v>
-      </c>
-      <c r="K20">
-        <f>SUMIF(Table1[AppClean], $J20, Table1[Day Duration (Minutes)])</f>
-        <v>3</v>
-      </c>
-      <c r="L20">
-        <f>SUMIF(Table1[AppClean], $J20, Table1[Notifications])</f>
-        <v>0</v>
-      </c>
-      <c r="M20">
-        <f>SUMIF(Table1[AppClean], $J20, Table1[Times Opened])</f>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="21" spans="2:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="21" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B21" s="1">
         <v>46084</v>
       </c>
@@ -1898,23 +1582,8 @@
         <f>TRIM(Table1[[#This Row],[App]])</f>
         <v>Signal</v>
       </c>
-      <c r="J21" t="str">
-        <v>Spotify</v>
-      </c>
-      <c r="K21">
-        <f>SUMIF(Table1[AppClean], $J21, Table1[Day Duration (Minutes)])</f>
-        <v>10</v>
-      </c>
-      <c r="L21">
-        <f>SUMIF(Table1[AppClean], $J21, Table1[Notifications])</f>
-        <v>2</v>
-      </c>
-      <c r="M21">
-        <f>SUMIF(Table1[AppClean], $J21, Table1[Times Opened])</f>
-        <v>13</v>
-      </c>
-    </row>
-    <row r="22" spans="2:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="22" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B22" s="1">
         <v>46084</v>
       </c>
@@ -1937,23 +1606,8 @@
         <f>TRIM(Table1[[#This Row],[App]])</f>
         <v>UP Banking</v>
       </c>
-      <c r="J22" t="str">
-        <v>Oto Music</v>
-      </c>
-      <c r="K22">
-        <f>SUMIF(Table1[AppClean], $J22, Table1[Day Duration (Minutes)])</f>
-        <v>4</v>
-      </c>
-      <c r="L22">
-        <f>SUMIF(Table1[AppClean], $J22, Table1[Notifications])</f>
-        <v>4</v>
-      </c>
-      <c r="M22">
-        <f>SUMIF(Table1[AppClean], $J22, Table1[Times Opened])</f>
-        <v>7</v>
-      </c>
-    </row>
-    <row r="23" spans="2:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="23" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B23" s="1">
         <v>46084</v>
       </c>
@@ -1976,23 +1630,8 @@
         <f>TRIM(Table1[[#This Row],[App]])</f>
         <v>Google Maps</v>
       </c>
-      <c r="J23" t="str">
-        <v>Mini Piano</v>
-      </c>
-      <c r="K23">
-        <f>SUMIF(Table1[AppClean], $J23, Table1[Day Duration (Minutes)])</f>
-        <v>3</v>
-      </c>
-      <c r="L23">
-        <f>SUMIF(Table1[AppClean], $J23, Table1[Notifications])</f>
-        <v>0</v>
-      </c>
-      <c r="M23">
-        <f>SUMIF(Table1[AppClean], $J23, Table1[Times Opened])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="2:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="24" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B24" s="1">
         <v>46084</v>
       </c>
@@ -2015,23 +1654,8 @@
         <f>TRIM(Table1[[#This Row],[App]])</f>
         <v>ChatGPT</v>
       </c>
-      <c r="J24" t="str">
-        <v>Petrol Spy</v>
-      </c>
-      <c r="K24">
-        <f>SUMIF(Table1[AppClean], $J24, Table1[Day Duration (Minutes)])</f>
-        <v>2</v>
-      </c>
-      <c r="L24">
-        <f>SUMIF(Table1[AppClean], $J24, Table1[Notifications])</f>
-        <v>0</v>
-      </c>
-      <c r="M24">
-        <f>SUMIF(Table1[AppClean], $J24, Table1[Times Opened])</f>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" spans="2:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="25" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B25" s="1">
         <v>46084</v>
       </c>
@@ -2054,23 +1678,8 @@
         <f>TRIM(Table1[[#This Row],[App]])</f>
         <v>Files</v>
       </c>
-      <c r="J25" t="str">
-        <v>GPS Tracker</v>
-      </c>
-      <c r="K25">
-        <f>SUMIF(Table1[AppClean], $J25, Table1[Day Duration (Minutes)])</f>
-        <v>6</v>
-      </c>
-      <c r="L25">
-        <f>SUMIF(Table1[AppClean], $J25, Table1[Notifications])</f>
-        <v>0</v>
-      </c>
-      <c r="M25">
-        <f>SUMIF(Table1[AppClean], $J25, Table1[Times Opened])</f>
-        <v>9</v>
-      </c>
-    </row>
-    <row r="26" spans="2:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="26" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B26" s="1">
         <v>46085</v>
       </c>
@@ -2093,23 +1702,8 @@
         <f>TRIM(Table1[[#This Row],[App]])</f>
         <v>Instagram</v>
       </c>
-      <c r="J26" t="str">
-        <v>HAOS</v>
-      </c>
-      <c r="K26">
-        <f>SUMIF(Table1[AppClean], $J26, Table1[Day Duration (Minutes)])</f>
-        <v>2</v>
-      </c>
-      <c r="L26">
-        <f>SUMIF(Table1[AppClean], $J26, Table1[Notifications])</f>
-        <v>8</v>
-      </c>
-      <c r="M26">
-        <f>SUMIF(Table1[AppClean], $J26, Table1[Times Opened])</f>
-        <v>6</v>
-      </c>
-    </row>
-    <row r="27" spans="2:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="27" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B27" s="1">
         <v>46085</v>
       </c>
@@ -2132,23 +1726,8 @@
         <f>TRIM(Table1[[#This Row],[App]])</f>
         <v>Firefox</v>
       </c>
-      <c r="J27" t="str">
-        <v>UniFi</v>
-      </c>
-      <c r="K27">
-        <f>SUMIF(Table1[AppClean], $J27, Table1[Day Duration (Minutes)])</f>
-        <v>9</v>
-      </c>
-      <c r="L27">
-        <f>SUMIF(Table1[AppClean], $J27, Table1[Notifications])</f>
-        <v>6</v>
-      </c>
-      <c r="M27">
-        <f>SUMIF(Table1[AppClean], $J27, Table1[Times Opened])</f>
-        <v>10</v>
-      </c>
-    </row>
-    <row r="28" spans="2:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="28" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B28" s="1">
         <v>46085</v>
       </c>
@@ -2171,23 +1750,8 @@
         <f>TRIM(Table1[[#This Row],[App]])</f>
         <v>Signal</v>
       </c>
-      <c r="J28" t="str">
-        <v>Net Analyzer</v>
-      </c>
-      <c r="K28">
-        <f>SUMIF(Table1[AppClean], $J28, Table1[Day Duration (Minutes)])</f>
-        <v>3</v>
-      </c>
-      <c r="L28">
-        <f>SUMIF(Table1[AppClean], $J28, Table1[Notifications])</f>
-        <v>0</v>
-      </c>
-      <c r="M28">
-        <f>SUMIF(Table1[AppClean], $J28, Table1[Times Opened])</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="29" spans="2:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="29" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B29" s="1">
         <v>46085</v>
       </c>
@@ -2211,7 +1775,7 @@
         <v>Youtube</v>
       </c>
     </row>
-    <row r="30" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="30" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B30" s="1">
         <v>46085</v>
       </c>
@@ -2235,7 +1799,7 @@
         <v>ChatGPT</v>
       </c>
     </row>
-    <row r="31" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="31" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B31" s="1">
         <v>46085</v>
       </c>
@@ -2259,7 +1823,7 @@
         <v>Gmail</v>
       </c>
     </row>
-    <row r="32" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="32" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B32" s="1">
         <v>46085</v>
       </c>
@@ -3078,12 +2642,8 @@
         <f>TRIM(Table1[[#This Row],[App]])</f>
         <v>Net Analyzer</v>
       </c>
-      <c r="J65" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="K65" s="3">
-        <v>71</v>
-      </c>
+      <c r="J65" s="3"/>
+      <c r="K65" s="3"/>
     </row>
     <row r="66" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B66" s="1">
@@ -3108,10 +2668,8 @@
         <f>TRIM(Table1[[#This Row],[App]])</f>
         <v>Phone</v>
       </c>
-      <c r="J66" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="K66" s="2"/>
+      <c r="J66" s="3"/>
+      <c r="K66" s="3"/>
     </row>
     <row r="67" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B67" s="1">
@@ -3136,9 +2694,7 @@
         <f>TRIM(Table1[[#This Row],[App]])</f>
         <v>Instagram</v>
       </c>
-      <c r="J67" s="3" t="s">
-        <v>10</v>
-      </c>
+      <c r="J67" s="3"/>
       <c r="K67" s="3"/>
     </row>
     <row r="68" spans="2:11" x14ac:dyDescent="0.2">
@@ -3164,12 +2720,8 @@
         <f>TRIM(Table1[[#This Row],[App]])</f>
         <v>Firefox</v>
       </c>
-      <c r="J68" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="K68" s="2">
-        <v>101</v>
-      </c>
+      <c r="J68" s="3"/>
+      <c r="K68" s="3"/>
     </row>
     <row r="69" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B69" s="1">
@@ -3194,12 +2746,8 @@
         <f>TRIM(Table1[[#This Row],[App]])</f>
         <v>Signal</v>
       </c>
-      <c r="J69" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="K69" s="3">
-        <v>22</v>
-      </c>
+      <c r="J69" s="3"/>
+      <c r="K69" s="3"/>
     </row>
     <row r="70" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B70" s="1">
@@ -3224,12 +2772,8 @@
         <f>TRIM(Table1[[#This Row],[App]])</f>
         <v>Phone</v>
       </c>
-      <c r="J70" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="K70" s="2">
-        <v>225</v>
-      </c>
+      <c r="J70" s="3"/>
+      <c r="K70" s="3"/>
     </row>
     <row r="71" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B71" s="1">
@@ -3254,12 +2798,8 @@
         <f>TRIM(Table1[[#This Row],[App]])</f>
         <v>UniFi</v>
       </c>
-      <c r="J71" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="K71" s="3">
-        <v>13</v>
-      </c>
+      <c r="J71" s="3"/>
+      <c r="K71" s="3"/>
     </row>
     <row r="72" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B72" s="1">
@@ -3284,12 +2824,8 @@
         <f>TRIM(Table1[[#This Row],[App]])</f>
         <v>ChatGPT</v>
       </c>
-      <c r="J72" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="K72" s="2">
-        <v>87</v>
-      </c>
+      <c r="J72" s="3"/>
+      <c r="K72" s="3"/>
     </row>
     <row r="73" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B73" s="1">
@@ -3314,12 +2850,8 @@
         <f>TRIM(Table1[[#This Row],[App]])</f>
         <v>Google Maps</v>
       </c>
-      <c r="J73" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="K73" s="3">
-        <v>54</v>
-      </c>
+      <c r="J73" s="3"/>
+      <c r="K73" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Data Sources.xlsx
+++ b/Data Sources.xlsx
@@ -680,11 +680,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -704,10 +703,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2642,8 +2637,8 @@
         <f>TRIM(Table1[[#This Row],[App]])</f>
         <v>Net Analyzer</v>
       </c>
-      <c r="J65" s="3"/>
-      <c r="K65" s="3"/>
+      <c r="J65" s="2"/>
+      <c r="K65" s="2"/>
     </row>
     <row r="66" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B66" s="1">
@@ -2668,8 +2663,8 @@
         <f>TRIM(Table1[[#This Row],[App]])</f>
         <v>Phone</v>
       </c>
-      <c r="J66" s="3"/>
-      <c r="K66" s="3"/>
+      <c r="J66" s="2"/>
+      <c r="K66" s="2"/>
     </row>
     <row r="67" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B67" s="1">
@@ -2694,8 +2689,8 @@
         <f>TRIM(Table1[[#This Row],[App]])</f>
         <v>Instagram</v>
       </c>
-      <c r="J67" s="3"/>
-      <c r="K67" s="3"/>
+      <c r="J67" s="2"/>
+      <c r="K67" s="2"/>
     </row>
     <row r="68" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B68" s="1">
@@ -2720,8 +2715,8 @@
         <f>TRIM(Table1[[#This Row],[App]])</f>
         <v>Firefox</v>
       </c>
-      <c r="J68" s="3"/>
-      <c r="K68" s="3"/>
+      <c r="J68" s="2"/>
+      <c r="K68" s="2"/>
     </row>
     <row r="69" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B69" s="1">
@@ -2746,8 +2741,8 @@
         <f>TRIM(Table1[[#This Row],[App]])</f>
         <v>Signal</v>
       </c>
-      <c r="J69" s="3"/>
-      <c r="K69" s="3"/>
+      <c r="J69" s="2"/>
+      <c r="K69" s="2"/>
     </row>
     <row r="70" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B70" s="1">
@@ -2772,8 +2767,8 @@
         <f>TRIM(Table1[[#This Row],[App]])</f>
         <v>Phone</v>
       </c>
-      <c r="J70" s="3"/>
-      <c r="K70" s="3"/>
+      <c r="J70" s="2"/>
+      <c r="K70" s="2"/>
     </row>
     <row r="71" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B71" s="1">
@@ -2798,8 +2793,8 @@
         <f>TRIM(Table1[[#This Row],[App]])</f>
         <v>UniFi</v>
       </c>
-      <c r="J71" s="3"/>
-      <c r="K71" s="3"/>
+      <c r="J71" s="2"/>
+      <c r="K71" s="2"/>
     </row>
     <row r="72" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B72" s="1">
@@ -2824,8 +2819,8 @@
         <f>TRIM(Table1[[#This Row],[App]])</f>
         <v>ChatGPT</v>
       </c>
-      <c r="J72" s="3"/>
-      <c r="K72" s="3"/>
+      <c r="J72" s="2"/>
+      <c r="K72" s="2"/>
     </row>
     <row r="73" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B73" s="1">
@@ -2850,8 +2845,8 @@
         <f>TRIM(Table1[[#This Row],[App]])</f>
         <v>Google Maps</v>
       </c>
-      <c r="J73" s="3"/>
-      <c r="K73" s="3"/>
+      <c r="J73" s="2"/>
+      <c r="K73" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
